--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE97703-D80E-4710-9DE5-68371876DC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400D94CC-852A-477F-A6C6-806803919C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50490" yWindow="680" windowWidth="24340" windowHeight="15680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11290" yWindow="4170" windowWidth="24170" windowHeight="12950" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -909,16 +909,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>78124</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>575081</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22960</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>82377</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>579334</xdr:colOff>
       <xdr:row>148</xdr:row>
-      <xdr:rowOff>29529</xdr:rowOff>
+      <xdr:rowOff>6569</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -935,7 +935,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22027037" y="22960"/>
+          <a:off x="23705646" y="0"/>
           <a:ext cx="4253" cy="23772134"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -4136,9 +4136,15 @@
       <c r="AG45" s="5">
         <v>20359</v>
       </c>
-      <c r="AH45" s="5"/>
-      <c r="AI45" s="5"/>
-      <c r="AJ45" s="5"/>
+      <c r="AH45" s="5">
+        <v>16750</v>
+      </c>
+      <c r="AI45" s="5">
+        <v>15473</v>
+      </c>
+      <c r="AJ45" s="5">
+        <v>20006</v>
+      </c>
       <c r="AK45" s="5"/>
       <c r="AL45" s="5"/>
       <c r="AT45" s="4">
@@ -4300,9 +4306,15 @@
       <c r="AG46" s="5">
         <v>417</v>
       </c>
-      <c r="AH46" s="5"/>
-      <c r="AI46" s="5"/>
-      <c r="AJ46" s="5"/>
+      <c r="AH46" s="5">
+        <v>542</v>
+      </c>
+      <c r="AI46" s="5">
+        <v>380</v>
+      </c>
+      <c r="AJ46" s="5">
+        <v>146</v>
+      </c>
       <c r="AK46" s="5"/>
       <c r="AL46" s="5"/>
       <c r="AT46" s="4">
@@ -4420,9 +4432,15 @@
       <c r="AG47" s="5">
         <v>429</v>
       </c>
-      <c r="AH47" s="5"/>
-      <c r="AI47" s="5"/>
-      <c r="AJ47" s="5"/>
+      <c r="AH47" s="5">
+        <v>401</v>
+      </c>
+      <c r="AI47" s="5">
+        <v>381</v>
+      </c>
+      <c r="AJ47" s="5">
+        <v>364</v>
+      </c>
       <c r="AK47" s="5"/>
       <c r="AL47" s="5"/>
       <c r="AT47" s="4">
@@ -4568,15 +4586,15 @@
       </c>
       <c r="AH48" s="7">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>17693</v>
       </c>
       <c r="AI48" s="7">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>16234</v>
       </c>
       <c r="AJ48" s="7">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>20516</v>
       </c>
       <c r="AK48" s="7">
         <f t="shared" si="41"/>
@@ -4745,9 +4763,15 @@
       <c r="AG49" s="5">
         <v>3415</v>
       </c>
-      <c r="AH49" s="5"/>
-      <c r="AI49" s="5"/>
-      <c r="AJ49" s="5"/>
+      <c r="AH49" s="5">
+        <v>3837</v>
+      </c>
+      <c r="AI49" s="5">
+        <v>2408</v>
+      </c>
+      <c r="AJ49" s="5">
+        <v>3139</v>
+      </c>
       <c r="AK49" s="5"/>
       <c r="AL49" s="5"/>
       <c r="AN49" s="4">
@@ -4874,9 +4898,15 @@
       <c r="AG50" s="5">
         <v>3475</v>
       </c>
-      <c r="AH50" s="5"/>
-      <c r="AI50" s="5"/>
-      <c r="AJ50" s="5"/>
+      <c r="AH50" s="5">
+        <v>3371</v>
+      </c>
+      <c r="AI50" s="5">
+        <v>3745</v>
+      </c>
+      <c r="AJ50" s="5">
+        <v>4581</v>
+      </c>
       <c r="AK50" s="5"/>
       <c r="AL50" s="5"/>
       <c r="AN50" s="4">
@@ -5031,15 +5061,15 @@
       </c>
       <c r="AH51" s="7">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>24901</v>
       </c>
       <c r="AI51" s="7">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>22387</v>
       </c>
       <c r="AJ51" s="7">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>28236</v>
       </c>
       <c r="AK51" s="7">
         <f t="shared" si="48"/>
@@ -10723,7 +10753,7 @@
         <v>19726</v>
       </c>
       <c r="X103" s="5">
-        <f t="shared" ref="X103:AG103" si="196">X104-X121</f>
+        <f t="shared" ref="X103:AF103" si="196">X104-X121</f>
         <v>25105</v>
       </c>
       <c r="Y103" s="5">
